--- a/ExcelToJsonWizard/excel_files/GameInfo.xlsx
+++ b/ExcelToJsonWizard/excel_files/GameInfo.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="73">
   <si>
     <t>key</t>
   </si>
@@ -22,10 +22,13 @@
     <t>description</t>
   </si>
   <si>
-    <t>spritePath</t>
+    <t>iconPath</t>
   </si>
   <si>
     <t>prefabPath</t>
+  </si>
+  <si>
+    <t>projectileSpritePath</t>
   </si>
   <si>
     <t>drop</t>
@@ -76,6 +79,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>List&lt;string&gt;</t>
+  </si>
+  <si>
     <t>float</t>
   </si>
   <si>
@@ -88,10 +94,13 @@
     <t>Description</t>
   </si>
   <si>
-    <t>SpritePath</t>
+    <t>IconPath</t>
   </si>
   <si>
     <t>PrefabPath</t>
+  </si>
+  <si>
+    <t>ProjectileSpritePath</t>
   </si>
   <si>
     <t>Percent</t>
@@ -128,6 +137,9 @@
   </si>
   <si>
     <t>알에서 막 깨어난 용.\n가끔식 자기 똥을 먹는다.</t>
+  </si>
+  <si>
+    <t>Br_baby_00,Br_baby_01</t>
   </si>
   <si>
     <t>어린용</t>
@@ -497,21 +509,22 @@
     <col customWidth="1" min="1" max="1" width="4.0"/>
     <col customWidth="1" min="2" max="2" width="11.88"/>
     <col customWidth="1" min="3" max="3" width="119.25"/>
-    <col customWidth="1" min="4" max="4" width="10.0"/>
+    <col customWidth="1" min="4" max="4" width="8.75"/>
     <col customWidth="1" min="5" max="5" width="10.63"/>
-    <col customWidth="1" min="6" max="6" width="7.38"/>
-    <col customWidth="1" min="7" max="7" width="11.75"/>
-    <col customWidth="1" min="8" max="8" width="10.88"/>
-    <col customWidth="1" min="9" max="9" width="10.5"/>
-    <col customWidth="1" min="10" max="10" width="16.5"/>
-    <col customWidth="1" min="11" max="11" width="17.0"/>
-    <col customWidth="1" min="12" max="12" width="10.63"/>
-    <col customWidth="1" min="13" max="13" width="11.13"/>
-    <col customWidth="1" min="14" max="15" width="10.5"/>
-    <col customWidth="1" min="16" max="16" width="18.0"/>
-    <col customWidth="1" min="17" max="17" width="19.88"/>
-    <col customWidth="1" min="18" max="18" width="17.13"/>
-    <col customWidth="1" min="19" max="19" width="16.25"/>
+    <col customWidth="1" min="6" max="6" width="19.88"/>
+    <col customWidth="1" min="7" max="7" width="7.38"/>
+    <col customWidth="1" min="8" max="8" width="11.75"/>
+    <col customWidth="1" min="9" max="9" width="10.88"/>
+    <col customWidth="1" min="10" max="10" width="10.5"/>
+    <col customWidth="1" min="11" max="11" width="16.5"/>
+    <col customWidth="1" min="12" max="12" width="17.0"/>
+    <col customWidth="1" min="13" max="13" width="10.63"/>
+    <col customWidth="1" min="14" max="14" width="11.13"/>
+    <col customWidth="1" min="15" max="16" width="10.5"/>
+    <col customWidth="1" min="17" max="17" width="18.0"/>
+    <col customWidth="1" min="18" max="18" width="19.88"/>
+    <col customWidth="1" min="19" max="19" width="17.13"/>
+    <col customWidth="1" min="20" max="20" width="16.25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -572,7 +585,9 @@
       <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2"/>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="U1" s="2"/>
       <c r="V1" s="2"/>
       <c r="W1" s="2"/>
@@ -582,63 +597,65 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="J2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="N2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="O2" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="T2" s="5"/>
+        <v>23</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="U2" s="5"/>
       <c r="V2" s="5"/>
       <c r="W2" s="5"/>
@@ -648,63 +665,65 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="T3" s="5"/>
+        <v>39</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="U3" s="5"/>
       <c r="V3" s="5"/>
       <c r="W3" s="5"/>
@@ -717,22 +736,22 @@
         <v>1.0</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F4" s="3">
-        <v>1.0</v>
+        <v>41</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="G4" s="3">
         <v>1.0</v>
       </c>
       <c r="H4" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="I4" s="3">
         <v>0.0</v>
-      </c>
-      <c r="I4" s="3">
-        <v>1.0</v>
       </c>
       <c r="J4" s="3">
         <v>1.0</v>
@@ -741,13 +760,13 @@
         <v>1.0</v>
       </c>
       <c r="L4" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M4" s="3">
         <v>0.0</v>
       </c>
       <c r="N4" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O4" s="3">
         <v>1.0</v>
@@ -764,7 +783,9 @@
       <c r="S4" s="3">
         <v>1.0</v>
       </c>
-      <c r="T4" s="5"/>
+      <c r="T4" s="3">
+        <v>1.0</v>
+      </c>
       <c r="U4" s="5"/>
       <c r="V4" s="5"/>
       <c r="W4" s="5"/>
@@ -777,22 +798,22 @@
         <v>2.0</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F5" s="3">
+        <v>44</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="3">
         <v>1.0</v>
       </c>
-      <c r="G5" s="3">
+      <c r="H5" s="3">
         <v>1.03</v>
       </c>
-      <c r="H5" s="3">
+      <c r="I5" s="3">
         <v>0.0</v>
-      </c>
-      <c r="I5" s="3">
-        <v>1.0</v>
       </c>
       <c r="J5" s="3">
         <v>1.0</v>
@@ -801,13 +822,13 @@
         <v>1.0</v>
       </c>
       <c r="L5" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M5" s="3">
         <v>0.0</v>
       </c>
       <c r="N5" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O5" s="3">
         <v>1.0</v>
@@ -824,7 +845,9 @@
       <c r="S5" s="3">
         <v>1.0</v>
       </c>
-      <c r="T5" s="5"/>
+      <c r="T5" s="3">
+        <v>1.0</v>
+      </c>
       <c r="U5" s="5"/>
       <c r="V5" s="5"/>
       <c r="W5" s="5"/>
@@ -837,22 +860,22 @@
         <v>3.0</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="3">
+      <c r="G6" s="3">
         <v>1.0</v>
       </c>
-      <c r="G6" s="3">
+      <c r="H6" s="3">
         <v>1.05</v>
       </c>
-      <c r="H6" s="3">
+      <c r="I6" s="3">
         <v>0.0</v>
-      </c>
-      <c r="I6" s="3">
-        <v>1.0</v>
       </c>
       <c r="J6" s="3">
         <v>1.0</v>
@@ -861,13 +884,13 @@
         <v>1.0</v>
       </c>
       <c r="L6" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M6" s="3">
         <v>0.0</v>
       </c>
       <c r="N6" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O6" s="3">
         <v>1.0</v>
@@ -884,7 +907,9 @@
       <c r="S6" s="3">
         <v>1.0</v>
       </c>
-      <c r="T6" s="5"/>
+      <c r="T6" s="3">
+        <v>1.0</v>
+      </c>
       <c r="U6" s="5"/>
       <c r="V6" s="5"/>
       <c r="W6" s="5"/>
@@ -897,22 +922,22 @@
         <v>4.0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" s="3">
-        <v>1.0</v>
+        <v>48</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="G7" s="3">
         <v>1.0</v>
       </c>
       <c r="H7" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="I7" s="3">
         <v>50.0</v>
-      </c>
-      <c r="I7" s="3">
-        <v>1.0</v>
       </c>
       <c r="J7" s="3">
         <v>1.0</v>
@@ -921,13 +946,13 @@
         <v>1.0</v>
       </c>
       <c r="L7" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M7" s="3">
         <v>0.0</v>
       </c>
       <c r="N7" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O7" s="3">
         <v>1.0</v>
@@ -944,7 +969,9 @@
       <c r="S7" s="3">
         <v>1.0</v>
       </c>
-      <c r="T7" s="5"/>
+      <c r="T7" s="3">
+        <v>1.0</v>
+      </c>
       <c r="U7" s="5"/>
       <c r="V7" s="5"/>
       <c r="W7" s="5"/>
@@ -957,37 +984,37 @@
         <v>5.0</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" s="3">
-        <v>1.0</v>
+        <v>50</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="G8" s="3">
         <v>1.0</v>
       </c>
       <c r="H8" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="I8" s="3">
         <v>0.0</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1.3</v>
-      </c>
-      <c r="J8" s="3">
-        <v>1.0</v>
       </c>
       <c r="K8" s="3">
         <v>1.0</v>
       </c>
       <c r="L8" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M8" s="3">
         <v>0.0</v>
       </c>
       <c r="N8" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O8" s="3">
         <v>1.0</v>
@@ -1004,7 +1031,9 @@
       <c r="S8" s="3">
         <v>1.0</v>
       </c>
-      <c r="T8" s="5"/>
+      <c r="T8" s="3">
+        <v>1.0</v>
+      </c>
       <c r="U8" s="5"/>
       <c r="V8" s="5"/>
       <c r="W8" s="5"/>
@@ -1017,22 +1046,22 @@
         <v>6.0</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" s="3">
+        <v>52</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="3">
         <v>0.9</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1.1</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>0.0</v>
-      </c>
-      <c r="I9" s="3">
-        <v>1.0</v>
       </c>
       <c r="J9" s="3">
         <v>1.0</v>
@@ -1041,13 +1070,13 @@
         <v>1.0</v>
       </c>
       <c r="L9" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M9" s="3">
         <v>0.0</v>
       </c>
       <c r="N9" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O9" s="3">
         <v>1.0</v>
@@ -1064,7 +1093,9 @@
       <c r="S9" s="3">
         <v>1.0</v>
       </c>
-      <c r="T9" s="5"/>
+      <c r="T9" s="3">
+        <v>1.0</v>
+      </c>
       <c r="U9" s="5"/>
       <c r="V9" s="5"/>
       <c r="W9" s="5"/>
@@ -1077,22 +1108,22 @@
         <v>7.0</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F10" s="3">
+        <v>54</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="3">
         <v>0.9</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1.0</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>0.0</v>
-      </c>
-      <c r="I10" s="3">
-        <v>1.0</v>
       </c>
       <c r="J10" s="3">
         <v>1.0</v>
@@ -1101,10 +1132,10 @@
         <v>1.0</v>
       </c>
       <c r="L10" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="M10" s="3">
         <v>0.0</v>
-      </c>
-      <c r="M10" s="3">
-        <v>1.0</v>
       </c>
       <c r="N10" s="3">
         <v>1.0</v>
@@ -1124,7 +1155,9 @@
       <c r="S10" s="3">
         <v>1.0</v>
       </c>
-      <c r="T10" s="5"/>
+      <c r="T10" s="3">
+        <v>1.0</v>
+      </c>
       <c r="U10" s="5"/>
       <c r="V10" s="5"/>
       <c r="W10" s="5"/>
@@ -1137,22 +1170,22 @@
         <v>8.0</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F11" s="3">
+        <v>56</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11" s="3">
         <v>0.9</v>
       </c>
-      <c r="G11" s="3">
+      <c r="H11" s="3">
         <v>1.0</v>
       </c>
-      <c r="H11" s="3">
+      <c r="I11" s="3">
         <v>0.0</v>
-      </c>
-      <c r="I11" s="3">
-        <v>1.0</v>
       </c>
       <c r="J11" s="3">
         <v>1.0</v>
@@ -1161,13 +1194,13 @@
         <v>1.0</v>
       </c>
       <c r="L11" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="M11" s="3">
         <v>-100.0</v>
       </c>
-      <c r="M11" s="3">
+      <c r="N11" s="3">
         <v>0.0</v>
-      </c>
-      <c r="N11" s="3">
-        <v>1.0</v>
       </c>
       <c r="O11" s="3">
         <v>1.0</v>
@@ -1184,7 +1217,9 @@
       <c r="S11" s="3">
         <v>1.0</v>
       </c>
-      <c r="T11" s="5"/>
+      <c r="T11" s="3">
+        <v>1.0</v>
+      </c>
       <c r="U11" s="5"/>
       <c r="V11" s="5"/>
       <c r="W11" s="5"/>
@@ -1197,37 +1232,37 @@
         <v>9.0</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F12" s="3">
+        <v>58</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="3">
         <v>0.9</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1.0</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>0.0</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1.0</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1.5</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2.0</v>
-      </c>
-      <c r="L12" s="3">
-        <v>0.0</v>
       </c>
       <c r="M12" s="3">
         <v>0.0</v>
       </c>
       <c r="N12" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O12" s="3">
         <v>1.0</v>
@@ -1244,7 +1279,9 @@
       <c r="S12" s="3">
         <v>1.0</v>
       </c>
-      <c r="T12" s="5"/>
+      <c r="T12" s="3">
+        <v>1.0</v>
+      </c>
       <c r="U12" s="5"/>
       <c r="V12" s="5"/>
       <c r="W12" s="5"/>
@@ -1257,37 +1294,37 @@
         <v>10.0</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F13" s="3">
+        <v>60</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" s="3">
         <v>0.8</v>
       </c>
-      <c r="G13" s="3">
+      <c r="H13" s="3">
         <v>1.0</v>
       </c>
-      <c r="H13" s="3">
+      <c r="I13" s="3">
         <v>0.0</v>
       </c>
-      <c r="I13" s="3">
+      <c r="J13" s="3">
         <v>1.0</v>
       </c>
-      <c r="J13" s="3">
+      <c r="K13" s="3">
         <v>1.8</v>
       </c>
-      <c r="K13" s="3">
+      <c r="L13" s="3">
         <v>2.3</v>
-      </c>
-      <c r="L13" s="3">
-        <v>0.0</v>
       </c>
       <c r="M13" s="3">
         <v>0.0</v>
       </c>
       <c r="N13" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O13" s="3">
         <v>1.0</v>
@@ -1304,7 +1341,9 @@
       <c r="S13" s="3">
         <v>1.0</v>
       </c>
-      <c r="T13" s="5"/>
+      <c r="T13" s="3">
+        <v>1.0</v>
+      </c>
       <c r="U13" s="5"/>
       <c r="V13" s="5"/>
       <c r="W13" s="5"/>
@@ -1317,22 +1356,22 @@
         <v>11.0</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F14" s="3">
+        <v>62</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G14" s="3">
         <v>0.8</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1.0</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>0.0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>1.0</v>
       </c>
       <c r="J14" s="3">
         <v>1.0</v>
@@ -1341,16 +1380,16 @@
         <v>1.0</v>
       </c>
       <c r="L14" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M14" s="3">
         <v>0.0</v>
       </c>
       <c r="N14" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="O14" s="3">
         <v>1.1</v>
-      </c>
-      <c r="O14" s="3">
-        <v>1.0</v>
       </c>
       <c r="P14" s="3">
         <v>1.0</v>
@@ -1364,7 +1403,9 @@
       <c r="S14" s="3">
         <v>1.0</v>
       </c>
-      <c r="T14" s="5"/>
+      <c r="T14" s="3">
+        <v>1.0</v>
+      </c>
       <c r="U14" s="5"/>
       <c r="V14" s="5"/>
       <c r="W14" s="5"/>
@@ -1377,37 +1418,37 @@
         <v>12.0</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F15" s="3">
+        <v>64</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15" s="3">
         <v>0.8</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1.0</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>0.0</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1.4</v>
-      </c>
-      <c r="J15" s="3">
-        <v>1.0</v>
       </c>
       <c r="K15" s="3">
         <v>1.0</v>
       </c>
       <c r="L15" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M15" s="3">
         <v>0.0</v>
       </c>
       <c r="N15" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O15" s="3">
         <v>1.0</v>
@@ -1424,7 +1465,9 @@
       <c r="S15" s="3">
         <v>1.0</v>
       </c>
-      <c r="T15" s="5"/>
+      <c r="T15" s="3">
+        <v>1.0</v>
+      </c>
       <c r="U15" s="5"/>
       <c r="V15" s="5"/>
       <c r="W15" s="5"/>
@@ -1437,22 +1480,22 @@
         <v>13.0</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F16" s="3">
+        <v>66</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="3">
         <v>0.8</v>
       </c>
-      <c r="G16" s="3">
+      <c r="H16" s="3">
         <v>1.0</v>
       </c>
-      <c r="H16" s="3">
+      <c r="I16" s="3">
         <v>0.0</v>
-      </c>
-      <c r="I16" s="3">
-        <v>1.0</v>
       </c>
       <c r="J16" s="3">
         <v>1.0</v>
@@ -1461,19 +1504,19 @@
         <v>1.0</v>
       </c>
       <c r="L16" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M16" s="3">
         <v>0.0</v>
       </c>
       <c r="N16" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="O16" s="3">
         <v>1.0</v>
       </c>
-      <c r="O16" s="3">
+      <c r="P16" s="3">
         <v>1.5</v>
-      </c>
-      <c r="P16" s="3">
-        <v>1.0</v>
       </c>
       <c r="Q16" s="3">
         <v>1.0</v>
@@ -1484,7 +1527,9 @@
       <c r="S16" s="3">
         <v>1.0</v>
       </c>
-      <c r="T16" s="5"/>
+      <c r="T16" s="3">
+        <v>1.0</v>
+      </c>
       <c r="U16" s="5"/>
       <c r="V16" s="5"/>
       <c r="W16" s="5"/>
@@ -1497,22 +1542,22 @@
         <v>14.0</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F17" s="3">
+        <v>68</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17" s="3">
         <v>0.8</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1.0</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>100.0</v>
-      </c>
-      <c r="I17" s="3">
-        <v>1.0</v>
       </c>
       <c r="J17" s="3">
         <v>1.0</v>
@@ -1521,13 +1566,13 @@
         <v>1.0</v>
       </c>
       <c r="L17" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M17" s="3">
         <v>0.0</v>
       </c>
       <c r="N17" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O17" s="3">
         <v>1.0</v>
@@ -1544,7 +1589,9 @@
       <c r="S17" s="3">
         <v>1.0</v>
       </c>
-      <c r="T17" s="5"/>
+      <c r="T17" s="3">
+        <v>1.0</v>
+      </c>
       <c r="U17" s="5"/>
       <c r="V17" s="5"/>
       <c r="W17" s="5"/>
@@ -1557,22 +1604,22 @@
         <v>15.0</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F18" s="3">
+        <v>70</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G18" s="3">
         <v>0.8</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1.15</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>0.0</v>
-      </c>
-      <c r="I18" s="3">
-        <v>1.0</v>
       </c>
       <c r="J18" s="3">
         <v>1.0</v>
@@ -1581,13 +1628,13 @@
         <v>1.0</v>
       </c>
       <c r="L18" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M18" s="3">
         <v>0.0</v>
       </c>
       <c r="N18" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O18" s="3">
         <v>1.0</v>
@@ -1604,7 +1651,9 @@
       <c r="S18" s="3">
         <v>1.0</v>
       </c>
-      <c r="T18" s="5"/>
+      <c r="T18" s="3">
+        <v>1.0</v>
+      </c>
       <c r="U18" s="5"/>
       <c r="V18" s="5"/>
       <c r="W18" s="5"/>
@@ -1617,22 +1666,22 @@
         <v>16.0</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F19" s="3">
+        <v>72</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G19" s="3">
         <v>0.8</v>
       </c>
-      <c r="G19" s="3">
+      <c r="H19" s="3">
         <v>1.3</v>
       </c>
-      <c r="H19" s="3">
+      <c r="I19" s="3">
         <v>0.0</v>
-      </c>
-      <c r="I19" s="3">
-        <v>1.0</v>
       </c>
       <c r="J19" s="3">
         <v>1.0</v>
@@ -1641,13 +1690,13 @@
         <v>1.0</v>
       </c>
       <c r="L19" s="3">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="M19" s="3">
         <v>0.0</v>
       </c>
       <c r="N19" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="O19" s="3">
         <v>1.0</v>
@@ -1664,7 +1713,9 @@
       <c r="S19" s="3">
         <v>1.0</v>
       </c>
-      <c r="T19" s="5"/>
+      <c r="T19" s="3">
+        <v>1.0</v>
+      </c>
       <c r="U19" s="5"/>
       <c r="V19" s="5"/>
       <c r="W19" s="5"/>

--- a/ExcelToJsonWizard/excel_files/GameInfo.xlsx
+++ b/ExcelToJsonWizard/excel_files/GameInfo.xlsx
@@ -4,6 +4,7 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="DragonsData" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="EnemyData" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="140">
   <si>
     <t>key</t>
   </si>
@@ -139,6 +140,12 @@
     <t>알에서 막 깨어난 용.\n가끔식 자기 똥을 먹는다.</t>
   </si>
   <si>
+    <t>Icon/Icon_Dragon_00</t>
+  </si>
+  <si>
+    <t>Dragons/BabyDragon</t>
+  </si>
+  <si>
     <t>Br_baby_00,Br_baby_01</t>
   </si>
   <si>
@@ -148,10 +155,22 @@
     <t>일명 초딩용.\n지치지 않고 뒤어 다니기 때문에 자주 만날 수 있다.</t>
   </si>
   <si>
+    <t>Icon/Icon_Dragon_01</t>
+  </si>
+  <si>
+    <t>Dragons/KidDragon</t>
+  </si>
+  <si>
     <t>사춘기용</t>
   </si>
   <si>
     <t>사춘기에 들어선 용.\n성격이 까칠하고 가끔씩 반항을 한다. 왕국 여기저기서 만날 수 있다.</t>
+  </si>
+  <si>
+    <t>Icon/Icon_Dragon_02</t>
+  </si>
+  <si>
+    <t>Dragons/TeenDragon</t>
   </si>
   <si>
     <t>빨간용</t>
@@ -160,10 +179,22 @@
     <t>성장이 끝난용.\n레드 드래곤으로 불린다.</t>
   </si>
   <si>
+    <t>Icon/Icon_Dragon_03</t>
+  </si>
+  <si>
+    <t>Dragons/RedDragon</t>
+  </si>
+  <si>
     <t>파란용</t>
   </si>
   <si>
     <t>레드 드래곤의 먼 친척. 오래전 북극에 갔다가 추워서 피부와 브레스가 파래졌다.\n해변가에서 일광용 하기를 좋아한다.</t>
+  </si>
+  <si>
+    <t>Icon/Icon_Dragon_04</t>
+  </si>
+  <si>
+    <t>Dragons/BlueDragon</t>
   </si>
   <si>
     <t>정글공룡</t>
@@ -172,10 +203,22 @@
     <t>정글에 사는 원시 드래곤.\n나뭇잎을 많이 먹어서 녹색 브레스를 발사함. 고대종 탐사팀에 의하여 발견되었으며, 공기 좋은 곳을 좋아한다고 함.</t>
   </si>
   <si>
+    <t>Icon/Icon_Dragon_05</t>
+  </si>
+  <si>
+    <t>Dragons/JungleDino</t>
+  </si>
+  <si>
     <t>북극공룡</t>
   </si>
   <si>
     <t>북그에 사는 원시 드래곤.\n빙하가 녹아서 살 곳이 점점 줄고있다. 고대종 탐사팀의 선박이 북극에 좌초되었을 때 발견되었다.</t>
+  </si>
+  <si>
+    <t>Icon/Icon_Dragon_06</t>
+  </si>
+  <si>
+    <t>Dragons/ArcticDino</t>
   </si>
   <si>
     <t>화산공룡</t>
@@ -184,10 +227,22 @@
     <t>화산 지대에서 발견된 원시 드래곤. 화산이 폭발해서 모든 생명체가 도망 중일때, 용암에서 온천을 즐겼다고 한다.</t>
   </si>
   <si>
+    <t>Icon/Icon_Dragon_07</t>
+  </si>
+  <si>
+    <t>Dragons/VolcanoDino</t>
+  </si>
+  <si>
     <t>하늘공룡</t>
   </si>
   <si>
     <t>날아다니는 원시 드래곤.\n최근 발견된 적은 없으나, 고대종 대백과사전에 그 존재가 기록되어 있으며 난폭한 성격을 지녔다고 하니 다가가지 말 것!</t>
+  </si>
+  <si>
+    <t>Icon/Icon_Dragon_08</t>
+  </si>
+  <si>
+    <t>Dragons/SkyDino</t>
   </si>
   <si>
     <t>사막비룡</t>
@@ -196,10 +251,22 @@
     <t>사막의 거친 모래 바람을 날린다.\n사막에서 만난다면 모래 바람때문에 길을 잃을 확률이 높아서, 사막 여행자들이 두려워하는 존재.</t>
   </si>
   <si>
+    <t>Icon/Icon_Dragon_09</t>
+  </si>
+  <si>
+    <t>Dragons/DessertWybern</t>
+  </si>
+  <si>
     <t>바다비룡</t>
   </si>
   <si>
     <t>시원한 바다 바람을 날려주는 비룡.\n인간들에게 인기가 많으나, 중지에서 잘 나오지 않는다.</t>
+  </si>
+  <si>
+    <t>Icon/Icon_Dragon_10</t>
+  </si>
+  <si>
+    <t>Dragons/SeatWybern</t>
   </si>
   <si>
     <t>숲비룡</t>
@@ -208,10 +275,19 @@
     <t>숲의 상쾌한 바람을 날리는 비룡.\n미세먼지를 날려주는 효과가 있음. 주로 둥지에서 생활한다.</t>
   </si>
   <si>
+    <t>Icon/Icon_Dragon_11</t>
+  </si>
+  <si>
+    <t>Dragons/ForestWybern</t>
+  </si>
+  <si>
     <t>얼음비룡</t>
   </si>
   <si>
     <t>보석같이 아름다운 얼음 결정을 만들어 낸다.\n하지만 매우 날카로우니 주의!!\n자신이 만든 얼음 둥지 꾸미기를 좋아한다.</t>
+  </si>
+  <si>
+    <t>Icon/Icon_Dragon_12</t>
   </si>
   <si>
     <t>번개비룡</t>
@@ -220,16 +296,142 @@
     <t>작지만 따가운 브레스를 발사한다. 만지면 찌릿찌릿 함.</t>
   </si>
   <si>
+    <t>Icon/Icon_Dragon_13</t>
+  </si>
+  <si>
     <t>화염비룡</t>
   </si>
   <si>
     <t>비룡중 가장 난폭한 성질을 가지고 있다. 가끔씩 마을이나 숲에 화재를 일으키곤 한다! 주로 둥지에서 생활한다.</t>
   </si>
   <si>
+    <t>Icon/Icon_Dragon_14</t>
+  </si>
+  <si>
     <t>노란용</t>
   </si>
   <si>
     <t>빨간용의 사촌 동생이다. 온 몸에서 정전기가 나오는 특이체질을 가지고 태어났다고 한다.</t>
+  </si>
+  <si>
+    <t>hp</t>
+  </si>
+  <si>
+    <t>coin</t>
+  </si>
+  <si>
+    <t>Hp</t>
+  </si>
+  <si>
+    <t>DropCoin</t>
+  </si>
+  <si>
+    <t>일반 고블린</t>
+  </si>
+  <si>
+    <t>Enemys/NormalGoblin</t>
+  </si>
+  <si>
+    <t>병사 고블린</t>
+  </si>
+  <si>
+    <t>Enemys/SoldierGoblin</t>
+  </si>
+  <si>
+    <t>마법사 고블린</t>
+  </si>
+  <si>
+    <t>Enemys/WizardGoblin</t>
+  </si>
+  <si>
+    <t>일반 슬라임</t>
+  </si>
+  <si>
+    <t>Enemys/NormalSlime</t>
+  </si>
+  <si>
+    <t>여자 슬라임</t>
+  </si>
+  <si>
+    <t>Enemys/FemaleSlime</t>
+  </si>
+  <si>
+    <t>독 슬라임</t>
+  </si>
+  <si>
+    <t>Enemys/PoisonSlime</t>
+  </si>
+  <si>
+    <t>날개 슬라임</t>
+  </si>
+  <si>
+    <t>Enemys/WingSlime</t>
+  </si>
+  <si>
+    <t>킹 슬라임</t>
+  </si>
+  <si>
+    <t>Enemys/KingSlime</t>
+  </si>
+  <si>
+    <t>일반 스켈레톤</t>
+  </si>
+  <si>
+    <t>Enemys/NormalSkeleton</t>
+  </si>
+  <si>
+    <t>병사 스켈레톤</t>
+  </si>
+  <si>
+    <t>Enemys/SoldierlSkeleton</t>
+  </si>
+  <si>
+    <t>암살자 스켈레톤</t>
+  </si>
+  <si>
+    <t>Enemys/AssasinSkeleton</t>
+  </si>
+  <si>
+    <t>불 원소</t>
+  </si>
+  <si>
+    <t>Enemys/FireElemental</t>
+  </si>
+  <si>
+    <t>물 원소</t>
+  </si>
+  <si>
+    <t>Enemys/WaterElemental</t>
+  </si>
+  <si>
+    <t>얼음 원소</t>
+  </si>
+  <si>
+    <t>Enemys/IceElemental</t>
+  </si>
+  <si>
+    <t>번개 원소</t>
+  </si>
+  <si>
+    <t>Enemys/ElectricityElemental</t>
+  </si>
+  <si>
+    <t>일반 오크</t>
+  </si>
+  <si>
+    <t>Enemys/NormalOrc</t>
+  </si>
+  <si>
+    <t>오크 전사</t>
+  </si>
+  <si>
+    <t>Enemys/SoldierOrc</t>
+  </si>
+  <si>
+    <t>주술사 오크</t>
+  </si>
+  <si>
+    <t>Enemys/WizardOrc</t>
   </si>
 </sst>
 </file>
@@ -276,7 +478,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -293,6 +495,9 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -302,6 +507,10 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -509,8 +718,8 @@
     <col customWidth="1" min="1" max="1" width="4.0"/>
     <col customWidth="1" min="2" max="2" width="11.88"/>
     <col customWidth="1" min="3" max="3" width="119.25"/>
-    <col customWidth="1" min="4" max="4" width="8.75"/>
-    <col customWidth="1" min="5" max="5" width="10.63"/>
+    <col customWidth="1" min="4" max="4" width="17.0"/>
+    <col customWidth="1" min="5" max="5" width="19.25"/>
     <col customWidth="1" min="6" max="6" width="19.88"/>
     <col customWidth="1" min="7" max="7" width="7.38"/>
     <col customWidth="1" min="8" max="8" width="11.75"/>
@@ -741,8 +950,14 @@
       <c r="C4" s="3" t="s">
         <v>41</v>
       </c>
+      <c r="D4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="F4" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G4" s="3">
         <v>1.0</v>
@@ -798,13 +1013,19 @@
         <v>2.0</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="G5" s="3">
         <v>1.0</v>
@@ -860,13 +1081,19 @@
         <v>3.0</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>46</v>
+        <v>50</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>52</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G6" s="3">
         <v>1.0</v>
@@ -922,13 +1149,19 @@
         <v>4.0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>48</v>
+        <v>54</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G7" s="3">
         <v>1.0</v>
@@ -984,13 +1217,19 @@
         <v>5.0</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>50</v>
+        <v>58</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G8" s="3">
         <v>1.0</v>
@@ -1046,13 +1285,19 @@
         <v>6.0</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>52</v>
+        <v>62</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>64</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G9" s="3">
         <v>0.9</v>
@@ -1108,13 +1353,19 @@
         <v>7.0</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>54</v>
+        <v>66</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>68</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G10" s="3">
         <v>0.9</v>
@@ -1170,13 +1421,19 @@
         <v>8.0</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>56</v>
+        <v>70</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>72</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G11" s="3">
         <v>0.9</v>
@@ -1232,13 +1489,19 @@
         <v>9.0</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>58</v>
+        <v>74</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>76</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G12" s="3">
         <v>0.9</v>
@@ -1294,13 +1557,19 @@
         <v>10.0</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>60</v>
+        <v>78</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>80</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G13" s="3">
         <v>0.8</v>
@@ -1356,13 +1625,19 @@
         <v>11.0</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>62</v>
+        <v>82</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>84</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G14" s="3">
         <v>0.8</v>
@@ -1418,13 +1693,19 @@
         <v>12.0</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>64</v>
+        <v>86</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G15" s="3">
         <v>0.8</v>
@@ -1480,13 +1761,16 @@
         <v>13.0</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>66</v>
+        <v>90</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>91</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G16" s="3">
         <v>0.8</v>
@@ -1542,13 +1826,16 @@
         <v>14.0</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>68</v>
+        <v>93</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G17" s="3">
         <v>0.8</v>
@@ -1604,13 +1891,16 @@
         <v>15.0</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>70</v>
+        <v>96</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G18" s="3">
         <v>0.8</v>
@@ -1666,13 +1956,13 @@
         <v>16.0</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G19" s="3">
         <v>0.8</v>
@@ -29194,4 +29484,379 @@
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="2" max="2" width="14.38"/>
+    <col customWidth="1" min="3" max="3" width="22.13"/>
+    <col customWidth="1" min="4" max="4" width="10.25"/>
+    <col customWidth="1" min="5" max="5" width="19.5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3">
+        <v>1001.0</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D4" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="E4" s="6">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3">
+        <v>1002.0</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D5" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="E5" s="6">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3">
+        <v>1003.0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" s="6">
+        <v>10.0</v>
+      </c>
+      <c r="E6" s="6">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3">
+        <v>1004.0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D7" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="E7" s="6">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3">
+        <v>1005.0</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D8" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="E8" s="6">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3">
+        <v>1006.0</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D9" s="6">
+        <v>10.0</v>
+      </c>
+      <c r="E9" s="6">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3">
+        <v>1007.0</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D10" s="6">
+        <v>12.0</v>
+      </c>
+      <c r="E10" s="6">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3">
+        <v>1008.0</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D11" s="6">
+        <v>14.0</v>
+      </c>
+      <c r="E11" s="6">
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3">
+        <v>1009.0</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D12" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="E12" s="6">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3">
+        <v>1010.0</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D13" s="6">
+        <v>10.0</v>
+      </c>
+      <c r="E13" s="6">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3">
+        <v>1011.0</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D14" s="6">
+        <v>14.0</v>
+      </c>
+      <c r="E14" s="6">
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3">
+        <v>1012.0</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D15" s="6">
+        <v>25.0</v>
+      </c>
+      <c r="E15" s="6">
+        <v>25.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3">
+        <v>1013.0</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D16" s="6">
+        <v>25.0</v>
+      </c>
+      <c r="E16" s="6">
+        <v>25.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3">
+        <v>1014.0</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D17" s="6">
+        <v>25.0</v>
+      </c>
+      <c r="E17" s="6">
+        <v>25.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3">
+        <v>1015.0</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D18" s="6">
+        <v>25.0</v>
+      </c>
+      <c r="E18" s="6">
+        <v>25.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3">
+        <v>1016.0</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D19" s="6">
+        <v>10.0</v>
+      </c>
+      <c r="E19" s="6">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3">
+        <v>1017.0</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D20" s="4">
+        <v>16.0</v>
+      </c>
+      <c r="E20" s="4">
+        <v>16.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3">
+        <v>1018.0</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D21" s="4">
+        <v>20.0</v>
+      </c>
+      <c r="E21" s="4">
+        <v>20.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/ExcelToJsonWizard/excel_files/GameInfo.xlsx
+++ b/ExcelToJsonWizard/excel_files/GameInfo.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="142">
   <si>
     <t>key</t>
   </si>
@@ -32,7 +32,7 @@
     <t>projectileSpritePath</t>
   </si>
   <si>
-    <t>drop</t>
+    <t>Drop</t>
   </si>
   <si>
     <t>damage</t>
@@ -320,10 +320,16 @@
     <t>coin</t>
   </si>
   <si>
+    <t>dropBonus</t>
+  </si>
+  <si>
     <t>Hp</t>
   </si>
   <si>
     <t>DropCoin</t>
+  </si>
+  <si>
+    <t>DropBonus</t>
   </si>
   <si>
     <t>일반 고블린</t>
@@ -438,7 +444,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -463,6 +469,12 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -478,7 +490,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -495,6 +507,9 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -960,7 +975,7 @@
         <v>44</v>
       </c>
       <c r="G4" s="3">
-        <v>1.0</v>
+        <v>0.9</v>
       </c>
       <c r="H4" s="3">
         <v>1.0</v>
@@ -1028,7 +1043,7 @@
         <v>44</v>
       </c>
       <c r="G5" s="3">
-        <v>1.0</v>
+        <v>0.89</v>
       </c>
       <c r="H5" s="3">
         <v>1.03</v>
@@ -1096,7 +1111,7 @@
         <v>44</v>
       </c>
       <c r="G6" s="3">
-        <v>1.0</v>
+        <v>0.87</v>
       </c>
       <c r="H6" s="3">
         <v>1.05</v>
@@ -1164,7 +1179,7 @@
         <v>44</v>
       </c>
       <c r="G7" s="3">
-        <v>1.0</v>
+        <v>0.84</v>
       </c>
       <c r="H7" s="3">
         <v>1.0</v>
@@ -1232,7 +1247,7 @@
         <v>44</v>
       </c>
       <c r="G8" s="3">
-        <v>1.0</v>
+        <v>0.8</v>
       </c>
       <c r="H8" s="3">
         <v>1.0</v>
@@ -1300,7 +1315,7 @@
         <v>44</v>
       </c>
       <c r="G9" s="3">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="H9" s="3">
         <v>1.1</v>
@@ -1368,7 +1383,7 @@
         <v>44</v>
       </c>
       <c r="G10" s="3">
-        <v>0.9</v>
+        <v>0.69</v>
       </c>
       <c r="H10" s="3">
         <v>1.0</v>
@@ -1436,7 +1451,7 @@
         <v>44</v>
       </c>
       <c r="G11" s="3">
-        <v>0.9</v>
+        <v>0.68</v>
       </c>
       <c r="H11" s="3">
         <v>1.0</v>
@@ -1504,7 +1519,7 @@
         <v>44</v>
       </c>
       <c r="G12" s="3">
-        <v>0.9</v>
+        <v>0.645</v>
       </c>
       <c r="H12" s="3">
         <v>1.0</v>
@@ -1572,7 +1587,7 @@
         <v>44</v>
       </c>
       <c r="G13" s="3">
-        <v>0.8</v>
+        <v>0.61</v>
       </c>
       <c r="H13" s="3">
         <v>1.0</v>
@@ -1640,7 +1655,7 @@
         <v>44</v>
       </c>
       <c r="G14" s="3">
-        <v>0.8</v>
+        <v>0.575</v>
       </c>
       <c r="H14" s="3">
         <v>1.0</v>
@@ -1708,7 +1723,7 @@
         <v>44</v>
       </c>
       <c r="G15" s="3">
-        <v>0.8</v>
+        <v>0.54</v>
       </c>
       <c r="H15" s="3">
         <v>1.0</v>
@@ -1773,7 +1788,7 @@
         <v>44</v>
       </c>
       <c r="G16" s="3">
-        <v>0.8</v>
+        <v>0.505</v>
       </c>
       <c r="H16" s="3">
         <v>1.0</v>
@@ -1838,7 +1853,7 @@
         <v>44</v>
       </c>
       <c r="G17" s="3">
-        <v>0.8</v>
+        <v>0.47</v>
       </c>
       <c r="H17" s="3">
         <v>1.0</v>
@@ -1903,7 +1918,7 @@
         <v>44</v>
       </c>
       <c r="G18" s="3">
-        <v>0.8</v>
+        <v>0.435</v>
       </c>
       <c r="H18" s="3">
         <v>1.15</v>
@@ -1965,7 +1980,7 @@
         <v>44</v>
       </c>
       <c r="G19" s="3">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="H19" s="3">
         <v>1.3</v>
@@ -2132,11 +2147,10 @@
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
+      <c r="G24" s="3"/>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
       <c r="J24" s="5"/>
-      <c r="K24" s="5"/>
       <c r="L24" s="5"/>
       <c r="M24" s="5"/>
       <c r="N24" s="5"/>
@@ -2380,7 +2394,7 @@
     <row r="33">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
+      <c r="C33" s="3"/>
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
@@ -29515,6 +29529,9 @@
       <c r="E1" s="1" t="s">
         <v>101</v>
       </c>
+      <c r="F1" s="6" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
@@ -29532,6 +29549,9 @@
       <c r="E2" s="4" t="s">
         <v>20</v>
       </c>
+      <c r="F2" s="4" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
@@ -29544,10 +29564,13 @@
         <v>28</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="4">
@@ -29555,16 +29578,19 @@
         <v>1001.0</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D4" s="6">
+        <v>107</v>
+      </c>
+      <c r="D4" s="7">
         <v>6.0</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="7">
         <v>6.0</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0.0</v>
       </c>
     </row>
     <row r="5">
@@ -29572,16 +29598,19 @@
         <v>1002.0</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D5" s="6">
+        <v>109</v>
+      </c>
+      <c r="D5" s="7">
         <v>8.0</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="7">
         <v>8.0</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0.01</v>
       </c>
     </row>
     <row r="6">
@@ -29589,16 +29618,19 @@
         <v>1003.0</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D6" s="6">
+        <v>111</v>
+      </c>
+      <c r="D6" s="7">
         <v>10.0</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="7">
         <v>10.0</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.02</v>
       </c>
     </row>
     <row r="7">
@@ -29606,16 +29638,19 @@
         <v>1004.0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="D7" s="6">
+        <v>113</v>
+      </c>
+      <c r="D7" s="7">
         <v>5.0</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="7">
         <v>5.0</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0.03</v>
       </c>
     </row>
     <row r="8">
@@ -29623,16 +29658,19 @@
         <v>1005.0</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="D8" s="6">
+        <v>115</v>
+      </c>
+      <c r="D8" s="7">
         <v>8.0</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="7">
         <v>8.0</v>
+      </c>
+      <c r="F8" s="4">
+        <v>0.04</v>
       </c>
     </row>
     <row r="9">
@@ -29640,16 +29678,19 @@
         <v>1006.0</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="D9" s="6">
+        <v>117</v>
+      </c>
+      <c r="D9" s="7">
         <v>10.0</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="7">
         <v>10.0</v>
+      </c>
+      <c r="F9" s="4">
+        <v>0.05</v>
       </c>
     </row>
     <row r="10">
@@ -29657,16 +29698,19 @@
         <v>1007.0</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="D10" s="6">
+        <v>119</v>
+      </c>
+      <c r="D10" s="7">
         <v>12.0</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="7">
         <v>12.0</v>
+      </c>
+      <c r="F10" s="4">
+        <v>0.06</v>
       </c>
     </row>
     <row r="11">
@@ -29674,16 +29718,19 @@
         <v>1008.0</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="D11" s="6">
+        <v>121</v>
+      </c>
+      <c r="D11" s="7">
         <v>14.0</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="7">
         <v>14.0</v>
+      </c>
+      <c r="F11" s="4">
+        <v>0.07</v>
       </c>
     </row>
     <row r="12">
@@ -29691,16 +29738,19 @@
         <v>1009.0</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D12" s="6">
+        <v>123</v>
+      </c>
+      <c r="D12" s="7">
         <v>6.0</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="7">
         <v>6.0</v>
+      </c>
+      <c r="F12" s="4">
+        <v>0.08</v>
       </c>
     </row>
     <row r="13">
@@ -29708,16 +29758,19 @@
         <v>1010.0</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="D13" s="6">
+        <v>125</v>
+      </c>
+      <c r="D13" s="7">
         <v>10.0</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="7">
         <v>10.0</v>
+      </c>
+      <c r="F13" s="4">
+        <v>0.09</v>
       </c>
     </row>
     <row r="14">
@@ -29725,16 +29778,19 @@
         <v>1011.0</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D14" s="6">
+        <v>127</v>
+      </c>
+      <c r="D14" s="7">
         <v>14.0</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="7">
         <v>14.0</v>
+      </c>
+      <c r="F14" s="4">
+        <v>0.1</v>
       </c>
     </row>
     <row r="15">
@@ -29742,16 +29798,19 @@
         <v>1012.0</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="D15" s="6">
+        <v>129</v>
+      </c>
+      <c r="D15" s="7">
         <v>25.0</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="7">
         <v>25.0</v>
+      </c>
+      <c r="F15" s="4">
+        <v>0.11</v>
       </c>
     </row>
     <row r="16">
@@ -29759,16 +29818,19 @@
         <v>1013.0</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="D16" s="6">
+        <v>131</v>
+      </c>
+      <c r="D16" s="7">
         <v>25.0</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="7">
         <v>25.0</v>
+      </c>
+      <c r="F16" s="4">
+        <v>0.12</v>
       </c>
     </row>
     <row r="17">
@@ -29776,16 +29838,19 @@
         <v>1014.0</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D17" s="6">
+        <v>133</v>
+      </c>
+      <c r="D17" s="7">
         <v>25.0</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="7">
         <v>25.0</v>
+      </c>
+      <c r="F17" s="4">
+        <v>0.13</v>
       </c>
     </row>
     <row r="18">
@@ -29793,16 +29858,19 @@
         <v>1015.0</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="D18" s="6">
+        <v>135</v>
+      </c>
+      <c r="D18" s="7">
         <v>25.0</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="7">
         <v>25.0</v>
+      </c>
+      <c r="F18" s="4">
+        <v>0.14</v>
       </c>
     </row>
     <row r="19">
@@ -29810,16 +29878,19 @@
         <v>1016.0</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D19" s="6">
+        <v>137</v>
+      </c>
+      <c r="D19" s="7">
         <v>10.0</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="7">
         <v>10.0</v>
+      </c>
+      <c r="F19" s="4">
+        <v>0.15</v>
       </c>
     </row>
     <row r="20">
@@ -29827,16 +29898,19 @@
         <v>1017.0</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D20" s="4">
         <v>16.0</v>
       </c>
       <c r="E20" s="4">
         <v>16.0</v>
+      </c>
+      <c r="F20" s="4">
+        <v>0.16</v>
       </c>
     </row>
     <row r="21">
@@ -29844,16 +29918,19 @@
         <v>1018.0</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D21" s="4">
         <v>20.0</v>
       </c>
       <c r="E21" s="4">
         <v>20.0</v>
+      </c>
+      <c r="F21" s="4">
+        <v>0.17</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelToJsonWizard/excel_files/GameInfo.xlsx
+++ b/ExcelToJsonWizard/excel_files/GameInfo.xlsx
@@ -32,7 +32,7 @@
     <t>projectileSpritePath</t>
   </si>
   <si>
-    <t>Drop</t>
+    <t>drop</t>
   </si>
   <si>
     <t>damage</t>

--- a/ExcelToJsonWizard/excel_files/GameInfo.xlsx
+++ b/ExcelToJsonWizard/excel_files/GameInfo.xlsx
@@ -3,8 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="DragonsData" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="EnemyData" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="DragonsData" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="EnemyData" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="143">
   <si>
     <t>key</t>
   </si>
@@ -314,6 +314,9 @@
     <t>빨간용의 사촌 동생이다. 온 몸에서 정전기가 나오는 특이체질을 가지고 태어났다고 한다.</t>
   </si>
   <si>
+    <t>Icon/Icon_Dragon_15</t>
+  </si>
+  <si>
     <t>hp</t>
   </si>
   <si>
@@ -527,6 +530,10 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1976,6 +1983,9 @@
       <c r="C19" s="3" t="s">
         <v>99</v>
       </c>
+      <c r="D19" s="4" t="s">
+        <v>100</v>
+      </c>
       <c r="F19" s="4" t="s">
         <v>44</v>
       </c>
@@ -29524,13 +29534,13 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2">
@@ -29564,13 +29574,13 @@
         <v>28</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4">
@@ -29578,10 +29588,10 @@
         <v>1001.0</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D4" s="7">
         <v>6.0</v>
@@ -29598,10 +29608,10 @@
         <v>1002.0</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D5" s="7">
         <v>8.0</v>
@@ -29618,10 +29628,10 @@
         <v>1003.0</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D6" s="7">
         <v>10.0</v>
@@ -29638,10 +29648,10 @@
         <v>1004.0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D7" s="7">
         <v>5.0</v>
@@ -29658,10 +29668,10 @@
         <v>1005.0</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D8" s="7">
         <v>8.0</v>
@@ -29678,10 +29688,10 @@
         <v>1006.0</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D9" s="7">
         <v>10.0</v>
@@ -29698,10 +29708,10 @@
         <v>1007.0</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D10" s="7">
         <v>12.0</v>
@@ -29718,10 +29728,10 @@
         <v>1008.0</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D11" s="7">
         <v>14.0</v>
@@ -29738,10 +29748,10 @@
         <v>1009.0</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D12" s="7">
         <v>6.0</v>
@@ -29758,10 +29768,10 @@
         <v>1010.0</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D13" s="7">
         <v>10.0</v>
@@ -29778,10 +29788,10 @@
         <v>1011.0</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D14" s="7">
         <v>14.0</v>
@@ -29798,10 +29808,10 @@
         <v>1012.0</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D15" s="7">
         <v>25.0</v>
@@ -29818,10 +29828,10 @@
         <v>1013.0</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D16" s="7">
         <v>25.0</v>
@@ -29838,10 +29848,10 @@
         <v>1014.0</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D17" s="7">
         <v>25.0</v>
@@ -29858,10 +29868,10 @@
         <v>1015.0</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D18" s="7">
         <v>25.0</v>
@@ -29878,10 +29888,10 @@
         <v>1016.0</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D19" s="7">
         <v>10.0</v>
@@ -29898,10 +29908,10 @@
         <v>1017.0</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D20" s="4">
         <v>16.0</v>
@@ -29918,10 +29928,10 @@
         <v>1018.0</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D21" s="4">
         <v>20.0</v>
